--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488274_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488274_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5278</v>
+        <v>3.8976</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4704</v>
+        <v>0.7417</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0574</v>
+        <v>3.1559</v>
       </c>
       <c r="G2" t="n">
         <v>3.1761</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5544</v>
+        <v>-0.0759</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8431</v>
+        <v>0.1144</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2888</v>
+        <v>-0.1903</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1899</v>
+        <v>3.417</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0299</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1601</v>
+        <v>3.3324</v>
       </c>
       <c r="G3" t="n">
         <v>3.0768</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5168</v>
+        <v>-0.2898</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2561</v>
+        <v>-0.2014</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2607</v>
+        <v>-0.0883</v>
       </c>
       <c r="V3" t="n">
         <v>0.63</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0425</v>
+        <v>2.7777</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7484</v>
+        <v>1.7052</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2942</v>
+        <v>1.0726</v>
       </c>
       <c r="G4" t="n">
         <v>2.3658</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8794</v>
+        <v>0.6146</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3608</v>
+        <v>0.1393</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9439</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3988</v>
+        <v>2.0836</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7716</v>
+        <v>-1.619</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1705</v>
+        <v>3.7026</v>
       </c>
       <c r="G5" t="n">
         <v>2.8248</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2601</v>
+        <v>-0.055</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8754</v>
+        <v>-0.7228</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1356</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3155</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0964</v>
+        <v>1.9312</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3667</v>
+        <v>2.1277</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2703</v>
+        <v>-0.1964</v>
       </c>
       <c r="G6" t="n">
         <v>1.9879</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6262</v>
+        <v>0.461</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6404</v>
+        <v>0.4014</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0142</v>
+        <v>0.0597</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2589</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1264</v>
+        <v>0.5734</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3227</v>
+        <v>0.0258</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4491</v>
+        <v>0.5476</v>
       </c>
       <c r="G9" t="n">
         <v>5.1039</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4778</v>
+        <v>-0.0308</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8207</v>
+        <v>-0.4722</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3429</v>
+        <v>0.4414</v>
       </c>
       <c r="V9" t="n">
         <v>-2.8321</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0946</v>
+        <v>0.094</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7938</v>
+        <v>-1.6959</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8884</v>
+        <v>1.7899</v>
       </c>
       <c r="G10" t="n">
         <v>0.4637</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9255</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3619</v>
+        <v>-0.2639</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5631</v>
+        <v>-0.6616</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4647</v>
+        <v>0.0396</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1937</v>
+        <v>-2.0131</v>
       </c>
       <c r="F11" t="n">
-        <v>1.729</v>
+        <v>2.0527</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2507</v>
+        <v>-0.4632</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5328000000000001</v>
+        <v>-0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7834</v>
+        <v>-0.3564</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2198</v>
+        <v>-1.0645</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0859</v>
+        <v>-1.1688</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3057</v>
+        <v>0.1043</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9692</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4469</v>
+        <v>1.062</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5223</v>
+        <v>-0.4607</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5285</v>
+        <v>-0.2002</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3619</v>
+        <v>0.2574</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1666</v>
+        <v>-0.4576</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5546</v>
+        <v>-0.2542</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4596</v>
+        <v>-3.6316</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9049</v>
+        <v>3.3774</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4632</v>
+        <v>-1.5378</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1068</v>
+        <v>0.2734</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3564</v>
+        <v>-1.8112</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0645</v>
+        <v>-2.8531</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1688</v>
+        <v>-1.134</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1043</v>
+        <v>-1.7192</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6012999999999999</v>
+        <v>1.3153</v>
       </c>
       <c r="N12" t="n">
-        <v>1.062</v>
+        <v>1.4073</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4607</v>
+        <v>-0.092</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>2.594</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2234</v>
+        <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7944</v>
+        <v>-0.3665</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.189</v>
+        <v>-0.4635</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6054</v>
+        <v>0.097</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2589</v>
+        <v>-0.9439</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5733</v>
+        <v>-0.315</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7313</v>
+        <v>-0.2869</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0348</v>
+        <v>-2.139</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3036</v>
+        <v>1.8521</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.5378</v>
+        <v>-0.2507</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2734</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8112</v>
+        <v>-0.7834</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8531</v>
+        <v>-1.2198</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.134</v>
+        <v>0.0859</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7192</v>
+        <v>-1.3057</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3153</v>
+        <v>0.9692</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4073</v>
+        <v>0.4469</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.092</v>
+        <v>0.5223</v>
       </c>
       <c r="P13" t="n">
-        <v>2.594</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>2.594</v>
+        <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8436</v>
+        <v>-0.3507</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8667</v>
+        <v>-0.3071</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0231</v>
+        <v>-0.0435</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9439</v>
+        <v>0.3144</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.6686</v>
+        <v>16.2158</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.240600000000001</v>
+        <v>-5.6934</v>
       </c>
       <c r="F14" t="n">
-        <v>21.9095</v>
+        <v>21.9094</v>
       </c>
       <c r="G14" t="n">
         <v>18.5792</v>
@@ -1519,13 +1519,13 @@
         <v>9.715000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>7.809700000000001</v>
+        <v>7.8097</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8990999999999998</v>
+        <v>0.8990999999999997</v>
       </c>
       <c r="L14" t="n">
-        <v>6.9106</v>
+        <v>6.910599999999999</v>
       </c>
       <c r="M14" t="n">
         <v>10.7696</v>
@@ -1546,13 +1546,13 @@
         <v>18.5287</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8965</v>
+        <v>-1.3494</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.0579</v>
+        <v>-1.5106</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1613</v>
+        <v>0.1616000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.7198</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2542</v>
+        <v>1.9021</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4793</v>
+        <v>1.5391</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7749</v>
+        <v>0.363</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8723</v>
+        <v>-0.8369</v>
       </c>
       <c r="H15" t="n">
-        <v>0.748</v>
+        <v>0.6314</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6203</v>
+        <v>-1.4683</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7683</v>
+        <v>-0.1707</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7683</v>
+        <v>0.3992</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.5699</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6405</v>
+        <v>-0.6663</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0203</v>
+        <v>0.2322</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6203</v>
+        <v>-0.8984</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0382</v>
+        <v>1.297</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0763</v>
+        <v>-0.1853</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0382</v>
+        <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5918</v>
+        <v>1.1276</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2146</v>
+        <v>0.3218</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3773</v>
+        <v>0.8058</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5727</v>
+        <v>0.3144</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5727</v>
+        <v>1.5733</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8877</v>
+        <v>1.0211</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4412</v>
+        <v>-1.3063</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4465</v>
+        <v>2.3274</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8369</v>
+        <v>-1.1821</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6314</v>
+        <v>-2.1129</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4683</v>
+        <v>0.9308</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1707</v>
+        <v>-0.1792</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3992</v>
+        <v>-1.4862</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5699</v>
+        <v>1.307</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6663</v>
+        <v>-1.0028</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2322</v>
+        <v>-0.6267</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8984</v>
+        <v>-0.3761</v>
       </c>
       <c r="P16" t="n">
-        <v>1.297</v>
+        <v>2.0382</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1853</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1132</v>
+        <v>0.1645</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2239</v>
+        <v>-0.3118</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8894</v>
+        <v>0.4763</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3144</v>
+        <v>0.0005</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2589</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7542</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6001</v>
+        <v>-0.9042</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3543</v>
+        <v>1.5721</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1821</v>
+        <v>1.4347</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1129</v>
+        <v>-0.2611</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9308</v>
+        <v>1.6958</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1792</v>
+        <v>1.0949</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4862</v>
+        <v>-0.2322</v>
       </c>
       <c r="L17" t="n">
-        <v>1.307</v>
+        <v>1.3271</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0028</v>
+        <v>0.3397</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6267</v>
+        <v>-0.029</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3761</v>
+        <v>0.3687</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1025</v>
+        <v>0.0305</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6056</v>
+        <v>-0.4607</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5031</v>
+        <v>0.4912</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6304999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4153</v>
+        <v>0.4903</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1001</v>
+        <v>-0.4793</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5154</v>
+        <v>0.9696</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4347</v>
+        <v>-0.8723</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2611</v>
+        <v>0.748</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6958</v>
+        <v>-1.6203</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0949</v>
+        <v>0.7683</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2322</v>
+        <v>0.7683</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3271</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3397</v>
+        <v>-1.6405</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.029</v>
+        <v>-0.0203</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3687</v>
+        <v>-1.6203</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-4.0763</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7411</v>
+        <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2221</v>
+        <v>1.828</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6566</v>
+        <v>1.256</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4345</v>
+        <v>0.572</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3144</v>
+        <v>1.5727</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>1.5727</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. GREVELS</t>
+          <t>R. VINCENT MAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8864</v>
+        <v>-0.296</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.885</v>
+        <v>0.4105</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0015</v>
+        <v>-0.7065</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7332</v>
+        <v>-1.2047</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2524</v>
+        <v>-1.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4808</v>
+        <v>-0.1166</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.4626</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.5455</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0829</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1219</v>
+        <v>-0.7421</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2524</v>
+        <v>-0.5426</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1306</v>
+        <v>-0.1996</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1532</v>
+        <v>-0.0177</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2736</v>
+        <v>-0.3858</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1204</v>
+        <v>0.3681</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VINCENT MAGO</t>
+          <t>H. GREVELS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1945</v>
+        <v>-0.788</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0791</v>
+        <v>-0.885</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1153</v>
+        <v>0.097</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2047</v>
+        <v>-0.7332</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0881</v>
+        <v>-0.2524</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1166</v>
+        <v>-0.4808</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4626</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5455</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0829</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7421</v>
+        <v>-0.1219</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5426</v>
+        <v>-0.2524</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1996</v>
+        <v>0.1306</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9162</v>
+        <v>-0.0547</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8754</v>
+        <v>-0.2736</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0408</v>
+        <v>0.2189</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2237</v>
+        <v>-1.4632</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.533</v>
+        <v>-2.435</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3093</v>
+        <v>0.9719</v>
       </c>
       <c r="G21" t="n">
         <v>0.1374</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9349</v>
+        <v>-0.1744</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3867</v>
+        <v>-0.2888</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5482</v>
+        <v>0.1144</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8583</v>
+        <v>-3.1762</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6699</v>
+        <v>-3.0616</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1885</v>
+        <v>-0.1146</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5434</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.538</v>
+        <v>0.2201</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4887</v>
+        <v>0.097</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9823</v>
+        <v>-3.239</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3011</v>
+        <v>-3.8115</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3188</v>
+        <v>0.5725</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2725</v>
@@ -2248,13 +2248,13 @@
         <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3768</v>
+        <v>0.3665</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5384</v>
+        <v>-0.0488</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1616</v>
+        <v>0.4153</v>
       </c>
       <c r="V23" t="n">
         <v>-0.63</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3395</v>
+        <v>-3.6534</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5169</v>
+        <v>-4.321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1774</v>
+        <v>0.6676</v>
       </c>
       <c r="G24" t="n">
         <v>-6.4484</v>
@@ -2326,13 +2326,13 @@
         <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3144</v>
+        <v>1.0004</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1691</v>
+        <v>0.365</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1452</v>
+        <v>0.6354</v>
       </c>
       <c r="V24" t="n">
         <v>3.4621</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4723</v>
+        <v>-4.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.0353</v>
+        <v>-6.5456</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5629</v>
+        <v>2.0457</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7736</v>
@@ -2404,13 +2404,13 @@
         <v>2.2234</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8458</v>
+        <v>0.1265</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.3224</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0338</v>
+        <v>0.4489</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.6456</v>
+        <v>-13.0345</v>
       </c>
       <c r="E26" t="n">
-        <v>-21.8</v>
+        <v>-21.7999</v>
       </c>
       <c r="F26" t="n">
-        <v>6.1542</v>
+        <v>8.765699999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-18.295</v>
@@ -2482,13 +2482,13 @@
         <v>14.4523</v>
       </c>
       <c r="S26" t="n">
-        <v>2.0059</v>
+        <v>4.6173</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.05200000000000005</v>
+        <v>-0.05210000000000009</v>
       </c>
       <c r="U26" t="n">
-        <v>2.0579</v>
+        <v>4.6694</v>
       </c>
       <c r="V26" t="n">
         <v>4.7197</v>
